--- a/Assets/Data/Dungeon2011.xlsx
+++ b/Assets/Data/Dungeon2011.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -55,10 +55,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -76,20 +76,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -99,39 +85,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -146,28 +100,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -181,9 +114,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -197,14 +176,20 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -214,9 +199,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -229,7 +229,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -241,19 +361,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -271,85 +397,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -361,55 +409,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,8 +426,58 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -450,49 +500,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -511,15 +520,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -528,145 +528,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1059,10 +1059,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="B2">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C2">
         <v>1</v>

--- a/Assets/Data/Dungeon2011.xlsx
+++ b/Assets/Data/Dungeon2011.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
@@ -55,10 +55,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -76,14 +76,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -91,47 +83,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -153,6 +106,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -162,7 +122,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -170,6 +145,37 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -183,15 +189,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -199,22 +207,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,7 +229,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -241,67 +259,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -319,24 +301,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -349,13 +313,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,7 +325,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -379,37 +379,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,26 +420,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -454,21 +434,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -520,6 +485,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -528,145 +528,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1624,7 +1624,9 @@
       <c r="H8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1695,9 +1697,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="1"/>
-      <c r="I9" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
         <v>8</v>
@@ -1906,7 +1906,9 @@
       <c r="H12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J12" s="1" t="s">
         <v>8</v>
       </c>

--- a/Assets/Data/Dungeon2011.xlsx
+++ b/Assets/Data/Dungeon2011.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="12">
   <si>
     <t>Id</t>
   </si>
@@ -41,6 +41,9 @@
     <t>InitDir</t>
   </si>
   <si>
+    <t>□</t>
+  </si>
+  <si>
     <t>■</t>
   </si>
   <si>
@@ -55,10 +58,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -76,8 +79,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -87,6 +91,105 @@
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -107,15 +210,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -123,98 +218,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,7 +232,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -241,13 +244,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,25 +262,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -307,7 +316,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -319,19 +352,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -343,55 +376,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,12 +416,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -420,6 +423,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -438,15 +456,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -458,15 +467,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -489,23 +489,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -520,6 +514,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -528,145 +531,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1071,13 +1074,13 @@
         <v>16</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>7</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1171,31 +1174,31 @@
         <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>8</v>
@@ -1206,7 +1209,9 @@
       <c r="P2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="1"/>
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
@@ -1246,31 +1251,31 @@
         <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>8</v>
@@ -1281,7 +1286,9 @@
       <c r="P3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q3" s="1"/>
+      <c r="Q3" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -1321,29 +1328,17 @@
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>8</v>
@@ -1354,7 +1349,9 @@
       <c r="P4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -1394,29 +1391,21 @@
         <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>8</v>
@@ -1427,7 +1416,9 @@
       <c r="P5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -1467,29 +1458,17 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>8</v>
@@ -1500,7 +1479,9 @@
       <c r="P6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -1540,29 +1521,17 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>8</v>
@@ -1573,7 +1542,9 @@
       <c r="P7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -1613,31 +1584,17 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>8</v>
@@ -1648,7 +1605,9 @@
       <c r="P8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="1"/>
+      <c r="Q8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -1688,25 +1647,17 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
       <c r="M9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>8</v>
@@ -1717,7 +1668,9 @@
       <c r="P9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="1"/>
+      <c r="Q9" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1757,25 +1710,21 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>8</v>
@@ -1786,7 +1735,9 @@
       <c r="P10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="1"/>
+      <c r="Q10" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -1826,25 +1777,17 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>8</v>
@@ -1855,7 +1798,9 @@
       <c r="P11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q11" s="1"/>
+      <c r="Q11" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -1895,31 +1840,29 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>8</v>
@@ -1930,7 +1873,9 @@
       <c r="P12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="1"/>
+      <c r="Q12" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
@@ -1970,29 +1915,31 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="J13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>8</v>
@@ -2003,7 +1950,9 @@
       <c r="P13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q13" s="1"/>
+      <c r="Q13" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
@@ -2043,29 +1992,29 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>8</v>
@@ -2076,7 +2025,9 @@
       <c r="P14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -2106,26 +2057,40 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -2155,28 +2120,44 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -2206,10 +2187,18 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -2217,11 +2206,21 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
+      <c r="M17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -2247,11 +2246,22 @@
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
     </row>
-    <row r="18" spans="2:41">
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+    <row r="18" spans="1:41">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -2259,11 +2269,21 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
+      <c r="M18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
@@ -2289,11 +2309,22 @@
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
     </row>
-    <row r="19" spans="2:41">
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+    <row r="19" spans="1:41">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -2301,11 +2332,21 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="M19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -2331,11 +2372,22 @@
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
     </row>
-    <row r="20" spans="2:41">
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+    <row r="20" spans="1:41">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -2343,11 +2395,21 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
+      <c r="M20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
@@ -2373,23 +2435,48 @@
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
     </row>
-    <row r="21" spans="2:41">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+    <row r="21" spans="1:41">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
+      <c r="M21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
@@ -2415,11 +2502,22 @@
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
     </row>
-    <row r="22" spans="2:41">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+    <row r="22" spans="1:41">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -2427,11 +2525,21 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -2457,23 +2565,56 @@
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
     </row>
-    <row r="23" spans="2:41">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
+    <row r="23" spans="1:41">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -2499,23 +2640,56 @@
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
     </row>
-    <row r="24" spans="2:41">
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
+    <row r="24" spans="1:41">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
@@ -2541,23 +2715,58 @@
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
     </row>
-    <row r="25" spans="2:41">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
+    <row r="25" spans="1:41">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
